--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -285,9 +285,6 @@
     <t>Media</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1216265318483681</t>
   </si>
   <si>
@@ -798,6 +795,9 @@
   </si>
   <si>
     <t>Preparación Materiales,Bodega:</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1216208498022089</t>
@@ -2326,7 +2326,7 @@
         <v>46266.50846133102</v>
       </c>
       <c r="D10" s="5">
-        <v>46274.16595439815</v>
+        <v>46279.749660347225</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2376,13 +2376,13 @@
       <c r="T10" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="U10" s="12" t="s">
-        <v>54</v>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" s="9">
         <v>46206.56956019676</v>
@@ -2394,7 +2394,7 @@
         <v>46266.50904626158</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
@@ -2424,10 +2424,10 @@
         <v>49</v>
       </c>
       <c r="O11" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P11" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="5">
         <v>46206.56957760417</v>
@@ -2449,7 +2449,7 @@
         <v>46266.509144456024</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2479,10 +2479,10 @@
         <v>49</v>
       </c>
       <c r="O12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="9">
         <v>46206.56959189815</v>
@@ -2504,7 +2504,7 @@
         <v>46266.50921978009</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2534,10 +2534,10 @@
         <v>49</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46206.56960495371</v>
@@ -2559,7 +2559,7 @@
         <v>46266.509278136575</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2589,10 +2589,10 @@
         <v>49</v>
       </c>
       <c r="O14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P14" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="9">
         <v>46206.569617824076</v>
@@ -2614,7 +2614,7 @@
         <v>46266.50933714121</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2644,10 +2644,10 @@
         <v>49</v>
       </c>
       <c r="O15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="5">
         <v>46206.56963048611</v>
@@ -2669,7 +2669,7 @@
         <v>46266.50939061343</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2699,10 +2699,10 @@
         <v>49</v>
       </c>
       <c r="O16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="9">
         <v>46206.56964277777</v>
@@ -2724,7 +2724,7 @@
         <v>46266.50945190972</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2754,10 +2754,10 @@
         <v>49</v>
       </c>
       <c r="O17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P17" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="P17" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -2767,7 +2767,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18" s="5">
         <v>46206.56965513889</v>
@@ -2779,7 +2779,7 @@
         <v>46266.50952775463</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2809,10 +2809,10 @@
         <v>49</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="9">
         <v>46206.569700810185</v>
@@ -2834,7 +2834,7 @@
         <v>46266.50959966435</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2864,10 +2864,10 @@
         <v>49</v>
       </c>
       <c r="O19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
@@ -2877,7 +2877,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20" s="5">
         <v>46204.78694056713</v>
@@ -2889,7 +2889,7 @@
         <v>46271.18686240741</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2913,7 +2913,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" s="9">
         <v>46204.787127372685</v>
@@ -2942,7 +2942,7 @@
         <v>46232.54893075231</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2963,19 +2963,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q21" s="9">
         <v>46217</v>
@@ -2995,7 +2995,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="5">
         <v>46204.787143009264</v>
@@ -3007,7 +3007,7 @@
         <v>46212.19074947917</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q22" s="5">
         <v>46211</v>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="9">
         <v>46204.78877271991</v>
@@ -3072,16 +3072,16 @@
         <v>46223.560216666665</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
@@ -3098,7 +3098,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" s="5">
         <v>46204.788881678236</v>
@@ -3127,16 +3127,16 @@
         <v>46223.56021195602</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I24" s="5">
         <v>46209</v>
@@ -3154,13 +3154,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q24" s="5">
         <v>46216</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B25" s="9">
         <v>46204.786945914355</v>
@@ -3192,7 +3192,7 @@
         <v>46270.90921540509</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -3216,7 +3216,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B26" s="5">
         <v>46204.78715721065</v>
@@ -3245,7 +3245,7 @@
         <v>46213.19381935185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3272,13 +3272,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46212</v>
@@ -3298,7 +3298,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="9">
         <v>46204.78716710648</v>
@@ -3310,7 +3310,7 @@
         <v>46260.88157532408</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3337,13 +3337,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>44</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q27" s="9">
         <v>46213</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B28" s="5">
         <v>46204.787177743056</v>
@@ -3375,16 +3375,16 @@
         <v>46260.88157600694</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I28" s="5">
         <v>46241</v>
@@ -3396,19 +3396,19 @@
         <v>26</v>
       </c>
       <c r="L28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="O28" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="M28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O28" s="6" t="s">
+      <c r="P28" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="Q28" s="5">
         <v>46244</v>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B29" s="9">
         <v>46204.79158200232</v>
@@ -3440,16 +3440,16 @@
         <v>46260.88157712963</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I29" s="9">
         <v>46241</v>
@@ -3461,19 +3461,19 @@
         <v>26</v>
       </c>
       <c r="L29" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O29" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="M29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="O29" s="10" t="s">
+      <c r="P29" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="Q29" s="9">
         <v>46244</v>
@@ -3493,7 +3493,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B30" s="5">
         <v>46204.79163886574</v>
@@ -3505,16 +3505,16 @@
         <v>46260.88150880787</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I30" s="5">
         <v>46241</v>
@@ -3532,13 +3532,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q30" s="5">
         <v>46244</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B31" s="9">
         <v>46204.7917447338</v>
@@ -3570,16 +3570,16 @@
         <v>46261.60066888889</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I31" s="9">
         <v>46241</v>
@@ -3597,13 +3597,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q31" s="9">
         <v>46244</v>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B32" s="5">
         <v>46204.78695173611</v>
@@ -3633,7 +3633,7 @@
         <v>46270.9090384375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3657,7 +3657,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B33" s="9">
         <v>46204.78719643518</v>
@@ -3680,16 +3680,16 @@
         <v>46274.15755173611</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3707,13 +3707,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q33" s="9">
         <v>46273</v>
@@ -3728,12 +3728,12 @@
         <v>33</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B34" s="5">
         <v>46204.7872006713</v>
@@ -3743,16 +3743,16 @@
         <v>46224.170235694444</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3770,13 +3770,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3784,15 +3784,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B35" s="9">
         <v>46204.787204837965</v>
@@ -3802,16 +3802,16 @@
         <v>46273.16818572917</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I35" s="9">
         <v>46225</v>
@@ -3829,13 +3829,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3843,15 +3843,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B36" s="5">
         <v>46204.78722327546</v>
@@ -3863,16 +3863,16 @@
         <v>46253.18898056713</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3890,10 +3890,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B37" s="9">
         <v>46204.78722760417</v>
@@ -3928,16 +3928,16 @@
         <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I37" s="9">
         <v>46213</v>
@@ -3955,13 +3955,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B38" s="5">
         <v>46204.787231689814</v>
@@ -3983,16 +3983,16 @@
         <v>46217.69452489584</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I38" s="5">
         <v>46224</v>
@@ -4010,13 +4010,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B39" s="9">
         <v>46204.78728243055</v>
@@ -4038,16 +4038,16 @@
         <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I39" s="9">
         <v>46224</v>
@@ -4065,13 +4065,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B40" s="5">
         <v>46204.78728729166</v>
@@ -4093,16 +4093,16 @@
         <v>46256.17364127315</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I40" s="5">
         <v>46245</v>
@@ -4120,13 +4120,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q40" s="5">
         <v>46255</v>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B41" s="9">
         <v>46204.787292175926</v>
@@ -4158,16 +4158,16 @@
         <v>46246.796326446754</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4185,13 +4185,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4199,15 +4199,15 @@
         <v>0</v>
       </c>
       <c r="T41" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B42" s="5">
         <v>46204.78730063657</v>
@@ -4219,16 +4219,16 @@
         <v>46251.58478496528</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I42" s="5">
         <v>46247</v>
@@ -4246,13 +4246,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4260,15 +4260,15 @@
         <v>0</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B43" s="9">
         <v>46204.793668136575</v>
@@ -4280,16 +4280,16 @@
         <v>46256.17364498843</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I43" s="9">
         <v>46245</v>
@@ -4307,10 +4307,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B44" s="5">
         <v>46204.794818298615</v>
@@ -4345,16 +4345,16 @@
         <v>46240.567830925924</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4372,13 +4372,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B45" s="9">
         <v>46204.794902430556</v>
@@ -4400,16 +4400,16 @@
         <v>46240.56791662037</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I45" s="9">
         <v>46247</v>
@@ -4427,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B46" s="5">
         <v>46204.7938509375</v>
@@ -4455,16 +4455,16 @@
         <v>46260.88172936343</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I46" s="5">
         <v>46245</v>
@@ -4482,10 +4482,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B47" s="9">
         <v>46204.795001412036</v>
@@ -4520,16 +4520,16 @@
         <v>46260.8816484375</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4547,13 +4547,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B48" s="5">
         <v>46204.795060543984</v>
@@ -4575,16 +4575,16 @@
         <v>46260.88170462963</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I48" s="5">
         <v>46247</v>
@@ -4602,13 +4602,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4618,7 +4618,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B49" s="9">
         <v>46204.7939687037</v>
@@ -4630,16 +4630,16 @@
         <v>46274.157551620374</v>
       </c>
       <c r="E49" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="I49" s="9">
         <v>46241</v>
@@ -4657,10 +4657,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B50" s="5">
         <v>46204.795132997686</v>
@@ -4695,16 +4695,16 @@
         <v>46238.52084538194</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4722,13 +4722,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4750,16 +4750,16 @@
         <v>46238.520887094906</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="I51" s="9">
         <v>46246</v>
@@ -4777,13 +4777,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4803,16 +4803,16 @@
         <v>46273.16825934028</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4828,10 +4828,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4854,7 +4854,7 @@
         <v>46271.30030990741</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4878,7 +4878,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4903,16 +4903,16 @@
         <v>46219.20085231481</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4930,13 +4930,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
@@ -4968,16 +4968,16 @@
         <v>46240.20805547453</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4995,13 +4995,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -5033,16 +5033,16 @@
         <v>46241.182524814816</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -5060,13 +5060,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -5096,16 +5096,16 @@
         <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -5123,13 +5123,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -5141,15 +5141,15 @@
         <v>0</v>
       </c>
       <c r="T57" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B58" s="5">
         <v>46205.8929956713</v>
@@ -5159,16 +5159,16 @@
         <v>46268.82877184028</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -5186,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5202,7 +5202,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B59" s="9">
         <v>46205.89308850694</v>
@@ -5212,16 +5212,16 @@
         <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5239,13 +5239,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46205.89321678241</v>
@@ -5265,16 +5265,16 @@
         <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5292,13 +5292,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46204.787330555555</v>
@@ -5320,7 +5320,7 @@
         <v>46260.88179142361</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5344,7 +5344,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46204.78733380787</v>
@@ -5373,16 +5373,16 @@
         <v>46260.881308842596</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5400,13 +5400,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q62" s="5">
         <v>46259</v>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B63" s="9">
         <v>46204.78733813658</v>
@@ -5438,16 +5438,16 @@
         <v>46262.17177444445</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5465,13 +5465,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="9">
         <v>46261</v>
@@ -5486,7 +5486,7 @@
         <v>33</v>
       </c>
       <c r="U63" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5509,10 +5509,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5530,10 +5530,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>218</v>
@@ -5574,10 +5574,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5595,7 +5595,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>217</v>
@@ -5616,7 +5616,7 @@
         <v>33</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5639,10 +5639,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5660,10 +5660,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>223</v>
@@ -5704,10 +5704,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5725,7 +5725,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>222</v>
@@ -5746,7 +5746,7 @@
         <v>33</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5858,7 +5858,7 @@
         <v>33</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5905,7 +5905,7 @@
         <v>226</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>226</v>
@@ -5940,7 +5940,7 @@
         <v>46260.585500416666</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5995,7 +5995,7 @@
         <v>46260.58551640046</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -6050,7 +6050,7 @@
         <v>46260.88124274305</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -6109,10 +6109,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -6133,7 +6133,7 @@
         <v>226</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>226</v>
@@ -6151,7 +6151,7 @@
         <v>33</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6168,16 +6168,16 @@
         <v>46260.58571837963</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -6196,7 +6196,7 @@
         <v>241</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>243</v>
@@ -6221,16 +6221,16 @@
         <v>46265.867035497686</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6249,7 +6249,7 @@
         <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>243</v>
@@ -6272,16 +6272,16 @@
         <v>46274.16820373843</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6300,7 +6300,7 @@
         <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>243</v>
@@ -6323,7 +6323,7 @@
         <v>46270.9214584838</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6376,10 +6376,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I79" s="9">
         <v>46210</v>
@@ -6397,10 +6397,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>250</v>
@@ -6418,7 +6418,7 @@
         <v>33</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6439,10 +6439,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6460,10 +6460,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>250</v>
@@ -6481,7 +6481,7 @@
         <v>33</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6502,10 +6502,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -6523,13 +6523,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>255</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q81" s="9">
         <v>46274</v>
@@ -6544,7 +6544,7 @@
         <v>33</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6559,16 +6559,16 @@
         <v>46274.16824643518</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6587,7 +6587,7 @@
         <v>254</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>257</v>
@@ -6610,16 +6610,16 @@
         <v>46274.16824774306</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6638,7 +6638,7 @@
         <v>254</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>259</v>
@@ -6661,16 +6661,16 @@
         <v>46274.1682487037</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6689,7 +6689,7 @@
         <v>254</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>257</v>
@@ -6712,16 +6712,16 @@
         <v>46274.16824969907</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6740,7 +6740,7 @@
         <v>254</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>257</v>
@@ -6763,16 +6763,16 @@
         <v>46274.168250601855</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6791,7 +6791,7 @@
         <v>254</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>257</v>
@@ -6814,16 +6814,16 @@
         <v>46274.16825158565</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6842,7 +6842,7 @@
         <v>254</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>257</v>
@@ -6865,16 +6865,16 @@
         <v>46274.168252731484</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6893,7 +6893,7 @@
         <v>254</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>257</v>
@@ -6916,16 +6916,16 @@
         <v>46274.168253807875</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6944,7 +6944,7 @@
         <v>254</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>257</v>
@@ -6967,16 +6967,16 @@
         <v>46274.1682546875</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6995,7 +6995,7 @@
         <v>254</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>257</v>
@@ -7024,10 +7024,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7045,10 +7045,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -7130,10 +7130,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I93" s="9">
         <v>46275</v>
@@ -7154,7 +7154,7 @@
         <v>270</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>270</v>
@@ -7172,7 +7172,7 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7189,16 +7189,16 @@
         <v>46268.82897372685</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -7219,7 +7219,7 @@
         <v>273</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>275</v>
@@ -7242,16 +7242,16 @@
         <v>46265.867042303245</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I95" s="9">
         <v>46275</v>
@@ -7272,7 +7272,7 @@
         <v>273</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>275</v>
@@ -7295,16 +7295,16 @@
         <v>46223.56049383101</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I96" s="5">
         <v>46275</v>
@@ -7325,7 +7325,7 @@
         <v>273</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>278</v>
@@ -7354,10 +7354,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I97" s="9">
         <v>46282</v>
@@ -7378,7 +7378,7 @@
         <v>270</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>270</v>
@@ -7396,7 +7396,7 @@
         <v>53</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7413,16 +7413,16 @@
         <v>46268.82912079861</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I98" s="5">
         <v>46282</v>
@@ -7466,16 +7466,16 @@
         <v>46238.48978101852</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I99" s="9">
         <v>46282</v>
@@ -7519,16 +7519,16 @@
         <v>46238.48978153935</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I100" s="5">
         <v>46282</v>
@@ -7552,7 +7552,7 @@
         <v>282</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46268.83232275463</v>
+        <v>46279.158440405095</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>287</v>
@@ -7578,10 +7578,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I101" s="9">
         <v>46286</v>
@@ -7602,7 +7602,7 @@
         <v>270</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>270</v>
@@ -7616,11 +7616,11 @@
       <c r="S101" s="10">
         <v>0</v>
       </c>
-      <c r="T101" s="7" t="s">
-        <v>122</v>
+      <c r="T101" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="U101" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7637,16 +7637,16 @@
         <v>46268.83231840278</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I102" s="5">
         <v>46286</v>
@@ -7690,16 +7690,16 @@
         <v>46238.489782488425</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I103" s="9">
         <v>46286</v>
@@ -7743,16 +7743,16 @@
         <v>46238.489782951394</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I104" s="5">
         <v>46286</v>
@@ -7802,10 +7802,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I105" s="9">
         <v>46287</v>
@@ -7826,7 +7826,7 @@
         <v>270</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>270</v>
@@ -7841,10 +7841,10 @@
         <v>0</v>
       </c>
       <c r="T105" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U105" s="12" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7861,16 +7861,16 @@
         <v>46268.8323234375</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I106" s="5">
         <v>46287</v>
@@ -7914,16 +7914,16 @@
         <v>46223.561678287035</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I107" s="9">
         <v>46287</v>
@@ -7967,16 +7967,16 @@
         <v>46223.56167766204</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I108" s="5">
         <v>46287</v>
@@ -8026,10 +8026,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I109" s="9">
         <v>46289</v>
@@ -8065,10 +8065,10 @@
         <v>0</v>
       </c>
       <c r="T109" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8085,16 +8085,16 @@
         <v>46268.832447175926</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I110" s="5">
         <v>46289</v>
@@ -8115,7 +8115,7 @@
         <v>301</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>304</v>
@@ -8144,10 +8144,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I111" s="9">
         <v>46289</v>
@@ -8168,7 +8168,7 @@
         <v>301</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>304</v>
@@ -8191,16 +8191,16 @@
         <v>46223.56179165509</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I112" s="5">
         <v>46289</v>
@@ -8221,7 +8221,7 @@
         <v>301</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>304</v>
@@ -8336,10 +8336,10 @@
         <v>0</v>
       </c>
       <c r="T114" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8354,7 +8354,7 @@
         <v>46268.83245145834</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8384,7 +8384,7 @@
         <v>312</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>317</v>
@@ -8407,7 +8407,7 @@
         <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8460,7 +8460,7 @@
         <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8490,7 +8490,7 @@
         <v>312</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>317</v>
@@ -8513,7 +8513,7 @@
         <v>46266.509050821754</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8543,7 +8543,7 @@
         <v>312</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>321</v>
@@ -8566,7 +8566,7 @@
         <v>46266.50914894676</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8596,7 +8596,7 @@
         <v>312</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>321</v>
@@ -8619,7 +8619,7 @@
         <v>46266.50928239583</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8649,7 +8649,7 @@
         <v>312</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>321</v>
@@ -8672,7 +8672,7 @@
         <v>46266.50922425926</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8702,7 +8702,7 @@
         <v>312</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>321</v>
@@ -8725,7 +8725,7 @@
         <v>46266.50934226852</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8755,7 +8755,7 @@
         <v>312</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>321</v>
@@ -8778,7 +8778,7 @@
         <v>46266.5093941088</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8808,7 +8808,7 @@
         <v>312</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>321</v>
@@ -8831,7 +8831,7 @@
         <v>46266.50945592593</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8861,7 +8861,7 @@
         <v>312</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>321</v>
@@ -8884,7 +8884,7 @@
         <v>46266.50953188658</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8914,7 +8914,7 @@
         <v>312</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>321</v>
@@ -8937,7 +8937,7 @@
         <v>46266.509606238425</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8967,7 +8967,7 @@
         <v>312</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>321</v>
@@ -8996,10 +8996,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I127" s="9">
         <v>46293</v>
@@ -9035,10 +9035,10 @@
         <v>0</v>
       </c>
       <c r="T127" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
@@ -9053,16 +9053,16 @@
         <v>46223.562056400464</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I128" s="5">
         <v>46293</v>
@@ -9083,7 +9083,7 @@
         <v>331</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>335</v>
@@ -9106,16 +9106,16 @@
         <v>46223.56205577546</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I129" s="9">
         <v>46293</v>
@@ -9136,7 +9136,7 @@
         <v>331</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>335</v>
@@ -9159,16 +9159,16 @@
         <v>46223.56205517361</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I130" s="5">
         <v>46293</v>
@@ -9189,7 +9189,7 @@
         <v>331</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>335</v>
@@ -9218,10 +9218,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I131" s="9">
         <v>46293</v>
@@ -9242,7 +9242,7 @@
         <v>331</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>340</v>
@@ -9271,10 +9271,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I132" s="5">
         <v>46293</v>
@@ -9295,7 +9295,7 @@
         <v>331</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>340</v>
@@ -9324,10 +9324,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I133" s="9">
         <v>46293</v>
@@ -9348,7 +9348,7 @@
         <v>331</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>340</v>
@@ -9377,10 +9377,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I134" s="5">
         <v>46293</v>
@@ -9401,7 +9401,7 @@
         <v>331</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>340</v>
@@ -9430,10 +9430,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I135" s="9">
         <v>46293</v>
@@ -9454,7 +9454,7 @@
         <v>331</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>340</v>
@@ -9483,10 +9483,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I136" s="5">
         <v>46293</v>
@@ -9507,7 +9507,7 @@
         <v>331</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>340</v>
@@ -9536,10 +9536,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H137" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I137" s="9">
         <v>46293</v>
@@ -9560,7 +9560,7 @@
         <v>331</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>340</v>
@@ -9589,10 +9589,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I138" s="5">
         <v>46293</v>
@@ -9613,7 +9613,7 @@
         <v>331</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>340</v>
@@ -9642,10 +9642,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H139" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I139" s="9">
         <v>46293</v>
@@ -9666,7 +9666,7 @@
         <v>331</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>340</v>
@@ -9734,10 +9734,10 @@
         <v>0</v>
       </c>
       <c r="T140" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U140" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
@@ -9782,7 +9782,7 @@
         <v>350</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>355</v>
@@ -9835,7 +9835,7 @@
         <v>350</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>355</v>
@@ -9888,7 +9888,7 @@
         <v>350</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>355</v>
@@ -10431,10 +10431,10 @@
         <v>0</v>
       </c>
       <c r="T153" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U153" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
@@ -11120,10 +11120,10 @@
         <v>0</v>
       </c>
       <c r="T166" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U166" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -11183,10 +11183,10 @@
         <v>0</v>
       </c>
       <c r="T167" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U167" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -11246,10 +11246,10 @@
         <v>0</v>
       </c>
       <c r="T168" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U168" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46268.82877262731</v>
+        <v>46280.14107565972</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>294</v>
@@ -7840,8 +7840,8 @@
       <c r="S105" s="10">
         <v>0</v>
       </c>
-      <c r="T105" s="7" t="s">
-        <v>121</v>
+      <c r="T105" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="U105" s="12" t="s">
         <v>215</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46206.67498217593</v>
+        <v>46281.16540657407</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>194</v>
@@ -5140,8 +5140,8 @@
       <c r="S57" s="10">
         <v>0</v>
       </c>
-      <c r="T57" s="7" t="s">
-        <v>121</v>
+      <c r="T57" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>117</v>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46274.165954375</v>
+        <v>46281.16821506944</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>273</v>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46265.867042303245</v>
+        <v>46281.16824315972</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>199</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46223.56049383101</v>
+        <v>46281.168244768516</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>199</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -282,9 +282,6 @@
     <t xml:space="preserve"> OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT' 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>1216265318483681</t>
   </si>
   <si>
@@ -744,6 +741,9 @@
   </si>
   <si>
     <t>OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1216239551129139</t>
@@ -2326,7 +2326,7 @@
         <v>46266.50846133102</v>
       </c>
       <c r="D10" s="5">
-        <v>46279.749660347225</v>
+        <v>46282.13446083333</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2373,8 +2373,8 @@
       <c r="S10" s="6">
         <v>1</v>
       </c>
-      <c r="T10" s="12" t="s">
-        <v>53</v>
+      <c r="T10" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U10" s="7" t="s">
         <v>27</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="9">
         <v>46206.56956019676</v>
@@ -2394,7 +2394,7 @@
         <v>46266.50904626158</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
@@ -2424,10 +2424,10 @@
         <v>49</v>
       </c>
       <c r="O11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P11" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="5">
         <v>46206.56957760417</v>
@@ -2449,7 +2449,7 @@
         <v>46266.509144456024</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2479,10 +2479,10 @@
         <v>49</v>
       </c>
       <c r="O12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="9">
         <v>46206.56959189815</v>
@@ -2504,7 +2504,7 @@
         <v>46266.50921978009</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2534,10 +2534,10 @@
         <v>49</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="5">
         <v>46206.56960495371</v>
@@ -2559,7 +2559,7 @@
         <v>46266.509278136575</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2589,10 +2589,10 @@
         <v>49</v>
       </c>
       <c r="O14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="P14" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="9">
         <v>46206.569617824076</v>
@@ -2614,7 +2614,7 @@
         <v>46266.50933714121</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2644,10 +2644,10 @@
         <v>49</v>
       </c>
       <c r="O15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B16" s="5">
         <v>46206.56963048611</v>
@@ -2669,7 +2669,7 @@
         <v>46266.50939061343</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2699,10 +2699,10 @@
         <v>49</v>
       </c>
       <c r="O16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="9">
         <v>46206.56964277777</v>
@@ -2724,7 +2724,7 @@
         <v>46266.50945190972</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2754,10 +2754,10 @@
         <v>49</v>
       </c>
       <c r="O17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P17" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="P17" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -2767,7 +2767,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="5">
         <v>46206.56965513889</v>
@@ -2779,7 +2779,7 @@
         <v>46266.50952775463</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2809,10 +2809,10 @@
         <v>49</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="9">
         <v>46206.569700810185</v>
@@ -2834,7 +2834,7 @@
         <v>46266.50959966435</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2864,10 +2864,10 @@
         <v>49</v>
       </c>
       <c r="O19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
@@ -2877,7 +2877,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B20" s="5">
         <v>46204.78694056713</v>
@@ -2889,7 +2889,7 @@
         <v>46271.18686240741</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2913,7 +2913,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" s="9">
         <v>46204.787127372685</v>
@@ -2942,7 +2942,7 @@
         <v>46232.54893075231</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2963,19 +2963,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q21" s="9">
         <v>46217</v>
@@ -2995,7 +2995,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="5">
         <v>46204.787143009264</v>
@@ -3007,7 +3007,7 @@
         <v>46212.19074947917</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q22" s="5">
         <v>46211</v>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" s="9">
         <v>46204.78877271991</v>
@@ -3072,16 +3072,16 @@
         <v>46223.560216666665</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
@@ -3098,7 +3098,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" s="5">
         <v>46204.788881678236</v>
@@ -3127,16 +3127,16 @@
         <v>46223.56021195602</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I24" s="5">
         <v>46209</v>
@@ -3154,13 +3154,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="5">
         <v>46216</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B25" s="9">
         <v>46204.786945914355</v>
@@ -3192,7 +3192,7 @@
         <v>46270.90921540509</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -3216,7 +3216,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B26" s="5">
         <v>46204.78715721065</v>
@@ -3245,7 +3245,7 @@
         <v>46213.19381935185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3272,13 +3272,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q26" s="5">
         <v>46212</v>
@@ -3298,7 +3298,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27" s="9">
         <v>46204.78716710648</v>
@@ -3310,7 +3310,7 @@
         <v>46260.88157532408</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3337,13 +3337,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>44</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q27" s="9">
         <v>46213</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B28" s="5">
         <v>46204.787177743056</v>
@@ -3375,16 +3375,16 @@
         <v>46260.88157600694</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I28" s="5">
         <v>46241</v>
@@ -3396,19 +3396,19 @@
         <v>26</v>
       </c>
       <c r="L28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O28" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="M28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O28" s="6" t="s">
+      <c r="P28" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="Q28" s="5">
         <v>46244</v>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B29" s="9">
         <v>46204.79158200232</v>
@@ -3440,16 +3440,16 @@
         <v>46260.88157712963</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I29" s="9">
         <v>46241</v>
@@ -3461,19 +3461,19 @@
         <v>26</v>
       </c>
       <c r="L29" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="O29" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="M29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="O29" s="10" t="s">
+      <c r="P29" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="Q29" s="9">
         <v>46244</v>
@@ -3493,7 +3493,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="5">
         <v>46204.79163886574</v>
@@ -3505,16 +3505,16 @@
         <v>46260.88150880787</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I30" s="5">
         <v>46241</v>
@@ -3532,13 +3532,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q30" s="5">
         <v>46244</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B31" s="9">
         <v>46204.7917447338</v>
@@ -3570,16 +3570,16 @@
         <v>46261.60066888889</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I31" s="9">
         <v>46241</v>
@@ -3597,13 +3597,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q31" s="9">
         <v>46244</v>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B32" s="5">
         <v>46204.78695173611</v>
@@ -3633,7 +3633,7 @@
         <v>46270.9090384375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3657,7 +3657,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B33" s="9">
         <v>46204.78719643518</v>
@@ -3680,16 +3680,16 @@
         <v>46274.15755173611</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3707,13 +3707,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q33" s="9">
         <v>46273</v>
@@ -3728,12 +3728,12 @@
         <v>33</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="5">
         <v>46204.7872006713</v>
@@ -3743,16 +3743,16 @@
         <v>46224.170235694444</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3770,13 +3770,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3784,15 +3784,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B35" s="9">
         <v>46204.787204837965</v>
@@ -3802,16 +3802,16 @@
         <v>46273.16818572917</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="I35" s="9">
         <v>46225</v>
@@ -3829,13 +3829,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3843,15 +3843,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B36" s="5">
         <v>46204.78722327546</v>
@@ -3863,16 +3863,16 @@
         <v>46253.18898056713</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3890,10 +3890,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B37" s="9">
         <v>46204.78722760417</v>
@@ -3928,16 +3928,16 @@
         <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="I37" s="9">
         <v>46213</v>
@@ -3955,13 +3955,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" s="5">
         <v>46204.787231689814</v>
@@ -3983,16 +3983,16 @@
         <v>46217.69452489584</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="I38" s="5">
         <v>46224</v>
@@ -4010,13 +4010,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B39" s="9">
         <v>46204.78728243055</v>
@@ -4038,16 +4038,16 @@
         <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="I39" s="9">
         <v>46224</v>
@@ -4065,13 +4065,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B40" s="5">
         <v>46204.78728729166</v>
@@ -4093,16 +4093,16 @@
         <v>46256.17364127315</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="I40" s="5">
         <v>46245</v>
@@ -4120,13 +4120,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q40" s="5">
         <v>46255</v>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B41" s="9">
         <v>46204.787292175926</v>
@@ -4158,16 +4158,16 @@
         <v>46246.796326446754</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4185,13 +4185,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4199,15 +4199,15 @@
         <v>0</v>
       </c>
       <c r="T41" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B42" s="5">
         <v>46204.78730063657</v>
@@ -4219,16 +4219,16 @@
         <v>46251.58478496528</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="I42" s="5">
         <v>46247</v>
@@ -4246,13 +4246,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4260,15 +4260,15 @@
         <v>0</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B43" s="9">
         <v>46204.793668136575</v>
@@ -4280,16 +4280,16 @@
         <v>46256.17364498843</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="I43" s="9">
         <v>46245</v>
@@ -4307,10 +4307,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B44" s="5">
         <v>46204.794818298615</v>
@@ -4345,16 +4345,16 @@
         <v>46240.567830925924</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4372,13 +4372,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B45" s="9">
         <v>46204.794902430556</v>
@@ -4400,16 +4400,16 @@
         <v>46240.56791662037</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="I45" s="9">
         <v>46247</v>
@@ -4427,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B46" s="5">
         <v>46204.7938509375</v>
@@ -4455,16 +4455,16 @@
         <v>46260.88172936343</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="I46" s="5">
         <v>46245</v>
@@ -4482,10 +4482,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B47" s="9">
         <v>46204.795001412036</v>
@@ -4520,16 +4520,16 @@
         <v>46260.8816484375</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4547,13 +4547,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B48" s="5">
         <v>46204.795060543984</v>
@@ -4575,16 +4575,16 @@
         <v>46260.88170462963</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="I48" s="5">
         <v>46247</v>
@@ -4602,13 +4602,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4618,7 +4618,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B49" s="9">
         <v>46204.7939687037</v>
@@ -4630,16 +4630,16 @@
         <v>46274.157551620374</v>
       </c>
       <c r="E49" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>166</v>
       </c>
       <c r="I49" s="9">
         <v>46241</v>
@@ -4657,10 +4657,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B50" s="5">
         <v>46204.795132997686</v>
@@ -4695,16 +4695,16 @@
         <v>46238.52084538194</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4722,13 +4722,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4750,16 +4750,16 @@
         <v>46238.520887094906</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>166</v>
       </c>
       <c r="I51" s="9">
         <v>46246</v>
@@ -4777,13 +4777,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4803,16 +4803,16 @@
         <v>46273.16825934028</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4828,10 +4828,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4854,7 +4854,7 @@
         <v>46271.30030990741</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4878,7 +4878,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4903,16 +4903,16 @@
         <v>46219.20085231481</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4930,13 +4930,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
@@ -4968,16 +4968,16 @@
         <v>46240.20805547453</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4995,13 +4995,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -5033,16 +5033,16 @@
         <v>46241.182524814816</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -5060,13 +5060,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -5096,16 +5096,16 @@
         <v>46281.16540657407</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>196</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -5123,13 +5123,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -5141,10 +5141,10 @@
         <v>0</v>
       </c>
       <c r="T57" s="12" t="s">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5165,10 +5165,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -5186,7 +5186,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>199</v>
@@ -5218,10 +5218,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>196</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5239,7 +5239,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>199</v>
@@ -5271,10 +5271,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5292,7 +5292,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>199</v>
@@ -5403,7 +5403,7 @@
         <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>211</v>
@@ -5444,10 +5444,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5533,7 +5533,7 @@
         <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>218</v>
@@ -5574,10 +5574,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5663,7 +5663,7 @@
         <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>223</v>
@@ -5704,10 +5704,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5905,7 +5905,7 @@
         <v>226</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>226</v>
@@ -6109,10 +6109,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -6133,7 +6133,7 @@
         <v>226</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>226</v>
@@ -6174,10 +6174,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -6227,10 +6227,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6278,10 +6278,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6400,7 +6400,7 @@
         <v>205</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>250</v>
@@ -6463,7 +6463,7 @@
         <v>205</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>250</v>
@@ -6544,7 +6544,7 @@
         <v>33</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6559,7 +6559,7 @@
         <v>46274.16824643518</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6587,7 +6587,7 @@
         <v>254</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>257</v>
@@ -6610,7 +6610,7 @@
         <v>46274.16824774306</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6638,7 +6638,7 @@
         <v>254</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>259</v>
@@ -6661,7 +6661,7 @@
         <v>46274.1682487037</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6689,7 +6689,7 @@
         <v>254</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>257</v>
@@ -6712,7 +6712,7 @@
         <v>46274.16824969907</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6740,7 +6740,7 @@
         <v>254</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>257</v>
@@ -6763,7 +6763,7 @@
         <v>46274.168250601855</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6791,7 +6791,7 @@
         <v>254</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>257</v>
@@ -6814,7 +6814,7 @@
         <v>46274.16825158565</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6842,7 +6842,7 @@
         <v>254</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>257</v>
@@ -6865,7 +6865,7 @@
         <v>46274.168252731484</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6893,7 +6893,7 @@
         <v>254</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>257</v>
@@ -6916,7 +6916,7 @@
         <v>46274.168253807875</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6944,7 +6944,7 @@
         <v>254</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>257</v>
@@ -6967,7 +6967,7 @@
         <v>46274.1682546875</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6995,7 +6995,7 @@
         <v>254</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>257</v>
@@ -7048,7 +7048,7 @@
         <v>205</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46281.16821506944</v>
+        <v>46282.134460381945</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>273</v>
@@ -7130,10 +7130,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I93" s="9">
         <v>46275</v>
@@ -7154,7 +7154,7 @@
         <v>270</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>270</v>
@@ -7168,8 +7168,8 @@
       <c r="S93" s="10">
         <v>0</v>
       </c>
-      <c r="T93" s="12" t="s">
-        <v>53</v>
+      <c r="T93" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U93" s="12" t="s">
         <v>215</v>
@@ -7195,10 +7195,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -7248,10 +7248,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I95" s="9">
         <v>46275</v>
@@ -7301,10 +7301,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I96" s="5">
         <v>46275</v>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46275.144512893516</v>
+        <v>46282.16799901621</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>280</v>
@@ -7354,10 +7354,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I97" s="9">
         <v>46282</v>
@@ -7378,7 +7378,7 @@
         <v>270</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>270</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="T97" s="12" t="s">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="U97" s="12" t="s">
         <v>215</v>
@@ -7419,10 +7419,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I98" s="5">
         <v>46282</v>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46238.48978101852</v>
+        <v>46282.16802197917</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>199</v>
@@ -7472,10 +7472,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I99" s="9">
         <v>46282</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46238.48978153935</v>
+        <v>46282.16802357639</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>199</v>
@@ -7525,10 +7525,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I100" s="5">
         <v>46282</v>
@@ -7578,10 +7578,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I101" s="9">
         <v>46286</v>
@@ -7602,7 +7602,7 @@
         <v>270</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>270</v>
@@ -7617,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="T101" s="12" t="s">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="U101" s="12" t="s">
         <v>215</v>
@@ -7643,10 +7643,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I102" s="5">
         <v>46286</v>
@@ -7696,10 +7696,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I103" s="9">
         <v>46286</v>
@@ -7749,10 +7749,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I104" s="5">
         <v>46286</v>
@@ -7802,10 +7802,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I105" s="9">
         <v>46287</v>
@@ -7826,7 +7826,7 @@
         <v>270</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>270</v>
@@ -7841,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="T105" s="12" t="s">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="U105" s="12" t="s">
         <v>215</v>
@@ -7867,10 +7867,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I106" s="5">
         <v>46287</v>
@@ -7920,10 +7920,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I107" s="9">
         <v>46287</v>
@@ -7973,10 +7973,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I108" s="5">
         <v>46287</v>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46268.83245050926</v>
+        <v>46282.15651052083</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>301</v>
@@ -8026,10 +8026,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I109" s="9">
         <v>46289</v>
@@ -8064,11 +8064,11 @@
       <c r="S109" s="10">
         <v>0</v>
       </c>
-      <c r="T109" s="7" t="s">
-        <v>121</v>
+      <c r="T109" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8091,10 +8091,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I110" s="5">
         <v>46289</v>
@@ -8144,10 +8144,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I111" s="9">
         <v>46289</v>
@@ -8197,10 +8197,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I112" s="5">
         <v>46289</v>
@@ -8336,10 +8336,10 @@
         <v>0</v>
       </c>
       <c r="T114" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8513,7 +8513,7 @@
         <v>46266.509050821754</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8543,7 +8543,7 @@
         <v>312</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>321</v>
@@ -8566,7 +8566,7 @@
         <v>46266.50914894676</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8596,7 +8596,7 @@
         <v>312</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>321</v>
@@ -8619,7 +8619,7 @@
         <v>46266.50928239583</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8649,7 +8649,7 @@
         <v>312</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>321</v>
@@ -8672,7 +8672,7 @@
         <v>46266.50922425926</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8702,7 +8702,7 @@
         <v>312</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>321</v>
@@ -8725,7 +8725,7 @@
         <v>46266.50934226852</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8755,7 +8755,7 @@
         <v>312</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>321</v>
@@ -8778,7 +8778,7 @@
         <v>46266.5093941088</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8808,7 +8808,7 @@
         <v>312</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>321</v>
@@ -8831,7 +8831,7 @@
         <v>46266.50945592593</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8861,7 +8861,7 @@
         <v>312</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>321</v>
@@ -8884,7 +8884,7 @@
         <v>46266.50953188658</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8914,7 +8914,7 @@
         <v>312</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>321</v>
@@ -8937,7 +8937,7 @@
         <v>46266.509606238425</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8967,7 +8967,7 @@
         <v>312</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>321</v>
@@ -8996,10 +8996,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I127" s="9">
         <v>46293</v>
@@ -9035,10 +9035,10 @@
         <v>0</v>
       </c>
       <c r="T127" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
@@ -9059,10 +9059,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I128" s="5">
         <v>46293</v>
@@ -9112,10 +9112,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I129" s="9">
         <v>46293</v>
@@ -9165,10 +9165,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I130" s="5">
         <v>46293</v>
@@ -9218,10 +9218,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I131" s="9">
         <v>46293</v>
@@ -9242,7 +9242,7 @@
         <v>331</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>340</v>
@@ -9271,10 +9271,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I132" s="5">
         <v>46293</v>
@@ -9295,7 +9295,7 @@
         <v>331</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>340</v>
@@ -9324,10 +9324,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I133" s="9">
         <v>46293</v>
@@ -9348,7 +9348,7 @@
         <v>331</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>340</v>
@@ -9377,10 +9377,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I134" s="5">
         <v>46293</v>
@@ -9401,7 +9401,7 @@
         <v>331</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>340</v>
@@ -9430,10 +9430,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I135" s="9">
         <v>46293</v>
@@ -9454,7 +9454,7 @@
         <v>331</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>340</v>
@@ -9483,10 +9483,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I136" s="5">
         <v>46293</v>
@@ -9507,7 +9507,7 @@
         <v>331</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>340</v>
@@ -9536,10 +9536,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H137" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I137" s="9">
         <v>46293</v>
@@ -9560,7 +9560,7 @@
         <v>331</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>340</v>
@@ -9589,10 +9589,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I138" s="5">
         <v>46293</v>
@@ -9613,7 +9613,7 @@
         <v>331</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>340</v>
@@ -9642,10 +9642,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H139" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I139" s="9">
         <v>46293</v>
@@ -9666,7 +9666,7 @@
         <v>331</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>340</v>
@@ -9734,10 +9734,10 @@
         <v>0</v>
       </c>
       <c r="T140" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U140" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
@@ -10431,10 +10431,10 @@
         <v>0</v>
       </c>
       <c r="T153" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U153" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
@@ -11120,10 +11120,10 @@
         <v>0</v>
       </c>
       <c r="T166" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U166" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -11183,10 +11183,10 @@
         <v>0</v>
       </c>
       <c r="T167" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U167" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -11246,10 +11246,10 @@
         <v>0</v>
       </c>
       <c r="T168" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U168" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
